--- a/01_analyses_states/Punjab/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Punjab/results/SoIB_summaries.xlsx
@@ -396,10 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C8">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>4</v>

--- a/01_analyses_states/Punjab/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Punjab/results/SoIB_summaries.xlsx
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C8">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>4</v>

--- a/01_analyses_states/Punjab/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Punjab/results/SoIB_summaries.xlsx
@@ -396,10 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C8">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -757,7 +757,7 @@
         <v>73</v>
       </c>
       <c r="E2">
-        <v>78.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="3">
@@ -773,10 +773,10 @@
         <v>29.1</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
     </row>
   </sheetData>
